--- a/outputs/Block2_TimeMachine_Target_Summary_v12.xlsx
+++ b/outputs/Block2_TimeMachine_Target_Summary_v12.xlsx
@@ -511,10 +511,10 @@
         <v>18</v>
       </c>
       <c r="D4">
-        <v>0.02263239999999976</v>
+        <v>0.02263239999999975</v>
       </c>
       <c r="E4">
-        <v>0.0002091999999993488</v>
+        <v>0.0002091999999993432</v>
       </c>
       <c r="F4">
         <v>10</v>
@@ -787,10 +787,10 @@
         <v>18</v>
       </c>
       <c r="D16">
-        <v>0.03052600000000001</v>
+        <v>0.03052600000000002</v>
       </c>
       <c r="E16">
-        <v>-4.280000000072559E-05</v>
+        <v>-4.280000000073114E-05</v>
       </c>
       <c r="F16">
         <v>10</v>
@@ -971,10 +971,10 @@
         <v>18</v>
       </c>
       <c r="D24">
-        <v>0.02636791788961459</v>
+        <v>0.0263679178896146</v>
       </c>
       <c r="E24">
-        <v>7.333760727237792E-05</v>
+        <v>7.333760727235017E-05</v>
       </c>
       <c r="F24">
         <v>10</v>

--- a/outputs/Block2_TimeMachine_Target_Summary_v12.xlsx
+++ b/outputs/Block2_TimeMachine_Target_Summary_v12.xlsx
@@ -787,10 +787,10 @@
         <v>18</v>
       </c>
       <c r="D16">
-        <v>0.03052600000000002</v>
+        <v>0.03052600000000003</v>
       </c>
       <c r="E16">
-        <v>-4.280000000073114E-05</v>
+        <v>-4.280000000072559E-05</v>
       </c>
       <c r="F16">
         <v>10</v>

--- a/outputs/Block2_TimeMachine_Target_Summary_v12.xlsx
+++ b/outputs/Block2_TimeMachine_Target_Summary_v12.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="17">
   <si>
     <t>Model</t>
   </si>
@@ -58,13 +58,7 @@
     <t>Derived Later</t>
   </si>
   <si>
-    <t>House Buckets</t>
-  </si>
-  <si>
     <t>Popular Vote</t>
-  </si>
-  <si>
-    <t>Senate Buckets</t>
   </si>
   <si>
     <t>Derived identity</t>
@@ -428,7 +422,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -462,13 +456,13 @@
         <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D2">
-        <v>10.925</v>
+        <v>14.45</v>
       </c>
       <c r="E2">
-        <v>-0.275</v>
+        <v>-5.5</v>
       </c>
       <c r="F2">
         <v>40</v>
@@ -485,16 +479,16 @@
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D3">
-        <v>5.725</v>
+        <v>0.02177959999999972</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>0.0002435999999993277</v>
       </c>
       <c r="F3">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -502,22 +496,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
         <v>15</v>
       </c>
-      <c r="C4" t="s">
-        <v>18</v>
-      </c>
       <c r="D4">
-        <v>0.02263239999999975</v>
+        <v>14.45</v>
       </c>
       <c r="E4">
-        <v>0.0002091999999993432</v>
+        <v>-5.5</v>
       </c>
       <c r="F4">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -525,22 +519,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
         <v>16</v>
       </c>
-      <c r="C5" t="s">
-        <v>18</v>
-      </c>
       <c r="D5">
-        <v>0.925</v>
+        <v>0.04010000000000001</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>-1.665334536937735E-17</v>
       </c>
       <c r="F5">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -548,19 +542,19 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D6">
-        <v>16.125</v>
+        <v>14.45</v>
       </c>
       <c r="E6">
-        <v>-0.075</v>
+        <v>-5.5</v>
       </c>
       <c r="F6">
         <v>40</v>
@@ -571,22 +565,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D7">
-        <v>7.45</v>
+        <v>0.01193820542365915</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>1.110223024625157E-17</v>
       </c>
       <c r="F7">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -594,22 +588,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" t="s">
         <v>15</v>
       </c>
-      <c r="C8" t="s">
-        <v>18</v>
-      </c>
       <c r="D8">
-        <v>0.04010000000000001</v>
+        <v>14.45</v>
       </c>
       <c r="E8">
-        <v>-1.665334536937735E-17</v>
+        <v>-5.5</v>
       </c>
       <c r="F8">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -617,22 +611,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" t="s">
         <v>16</v>
       </c>
-      <c r="C9" t="s">
-        <v>18</v>
-      </c>
       <c r="D9">
-        <v>1.1</v>
+        <v>0.02858919999999997</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>1.71999999992678E-05</v>
       </c>
       <c r="F9">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -640,19 +634,19 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B10" t="s">
         <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D10">
-        <v>8.925000000000001</v>
+        <v>14.45</v>
       </c>
       <c r="E10">
-        <v>-0.275</v>
+        <v>-5.5</v>
       </c>
       <c r="F10">
         <v>40</v>
@@ -663,22 +657,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D11">
-        <v>4.925</v>
+        <v>0.02235382843390595</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>-0.0004653821548390669</v>
       </c>
       <c r="F11">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -686,22 +680,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" t="s">
         <v>15</v>
       </c>
-      <c r="C12" t="s">
-        <v>18</v>
-      </c>
       <c r="D12">
-        <v>0.01193820542365915</v>
+        <v>14.45</v>
       </c>
       <c r="E12">
-        <v>1.110223024625157E-17</v>
+        <v>-5.5</v>
       </c>
       <c r="F12">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -709,300 +703,24 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" t="s">
         <v>16</v>
       </c>
-      <c r="C13" t="s">
-        <v>18</v>
-      </c>
       <c r="D13">
-        <v>0.8</v>
+        <v>0.02470934877672151</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>0.0001066140499440593</v>
       </c>
       <c r="F13">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" t="s">
-        <v>10</v>
-      </c>
-      <c r="B14" t="s">
-        <v>13</v>
-      </c>
-      <c r="C14" t="s">
-        <v>17</v>
-      </c>
-      <c r="D14">
-        <v>12.925</v>
-      </c>
-      <c r="E14">
-        <v>-0.275</v>
-      </c>
-      <c r="F14">
-        <v>40</v>
-      </c>
-      <c r="G14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B15" t="s">
-        <v>14</v>
-      </c>
-      <c r="C15" t="s">
-        <v>18</v>
-      </c>
-      <c r="D15">
-        <v>6.375</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-      <c r="F15">
-        <v>80</v>
-      </c>
-      <c r="G15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16" t="s">
-        <v>10</v>
-      </c>
-      <c r="B16" t="s">
-        <v>15</v>
-      </c>
-      <c r="C16" t="s">
-        <v>18</v>
-      </c>
-      <c r="D16">
-        <v>0.03052600000000003</v>
-      </c>
-      <c r="E16">
-        <v>-4.280000000072559E-05</v>
-      </c>
-      <c r="F16">
-        <v>10</v>
-      </c>
-      <c r="G16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" t="s">
-        <v>10</v>
-      </c>
-      <c r="B17" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" t="s">
-        <v>18</v>
-      </c>
-      <c r="D17">
-        <v>0.975</v>
-      </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-      <c r="F17">
-        <v>80</v>
-      </c>
-      <c r="G17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" t="s">
-        <v>11</v>
-      </c>
-      <c r="B18" t="s">
-        <v>13</v>
-      </c>
-      <c r="C18" t="s">
-        <v>17</v>
-      </c>
-      <c r="D18">
-        <v>8.925000000000001</v>
-      </c>
-      <c r="E18">
-        <v>-0.275</v>
-      </c>
-      <c r="F18">
-        <v>40</v>
-      </c>
-      <c r="G18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" t="s">
-        <v>11</v>
-      </c>
-      <c r="B19" t="s">
-        <v>14</v>
-      </c>
-      <c r="C19" t="s">
-        <v>18</v>
-      </c>
-      <c r="D19">
-        <v>4.925</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-      <c r="F19">
-        <v>80</v>
-      </c>
-      <c r="G19">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20" t="s">
-        <v>11</v>
-      </c>
-      <c r="B20" t="s">
-        <v>15</v>
-      </c>
-      <c r="C20" t="s">
-        <v>18</v>
-      </c>
-      <c r="D20">
-        <v>0.01634036927331421</v>
-      </c>
-      <c r="E20">
-        <v>-0.0001847012506733137</v>
-      </c>
-      <c r="F20">
-        <v>10</v>
-      </c>
-      <c r="G20">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21" t="s">
-        <v>11</v>
-      </c>
-      <c r="B21" t="s">
-        <v>16</v>
-      </c>
-      <c r="C21" t="s">
-        <v>18</v>
-      </c>
-      <c r="D21">
-        <v>0.8</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-      <c r="F21">
-        <v>80</v>
-      </c>
-      <c r="G21">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22" t="s">
-        <v>12</v>
-      </c>
-      <c r="B22" t="s">
-        <v>13</v>
-      </c>
-      <c r="C22" t="s">
-        <v>17</v>
-      </c>
-      <c r="D22">
-        <v>11.675</v>
-      </c>
-      <c r="E22">
-        <v>-0.275</v>
-      </c>
-      <c r="F22">
-        <v>40</v>
-      </c>
-      <c r="G22">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23" t="s">
-        <v>12</v>
-      </c>
-      <c r="B23" t="s">
-        <v>14</v>
-      </c>
-      <c r="C23" t="s">
-        <v>18</v>
-      </c>
-      <c r="D23">
-        <v>6.025</v>
-      </c>
-      <c r="E23">
-        <v>0</v>
-      </c>
-      <c r="F23">
-        <v>80</v>
-      </c>
-      <c r="G23">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24" t="s">
-        <v>12</v>
-      </c>
-      <c r="B24" t="s">
-        <v>15</v>
-      </c>
-      <c r="C24" t="s">
-        <v>18</v>
-      </c>
-      <c r="D24">
-        <v>0.0263679178896146</v>
-      </c>
-      <c r="E24">
-        <v>7.333760727235017E-05</v>
-      </c>
-      <c r="F24">
-        <v>10</v>
-      </c>
-      <c r="G24">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25" t="s">
-        <v>12</v>
-      </c>
-      <c r="B25" t="s">
-        <v>16</v>
-      </c>
-      <c r="C25" t="s">
-        <v>18</v>
-      </c>
-      <c r="D25">
-        <v>0.9</v>
-      </c>
-      <c r="E25">
-        <v>0</v>
-      </c>
-      <c r="F25">
-        <v>80</v>
-      </c>
-      <c r="G25">
         <v>5</v>
       </c>
     </row>

--- a/outputs/Block2_TimeMachine_Target_Summary_v12.xlsx
+++ b/outputs/Block2_TimeMachine_Target_Summary_v12.xlsx
@@ -715,7 +715,7 @@
         <v>0.02470934877672151</v>
       </c>
       <c r="E13">
-        <v>0.0001066140499440593</v>
+        <v>0.0001066140499440371</v>
       </c>
       <c r="F13">
         <v>10</v>

--- a/outputs/Block2_TimeMachine_Target_Summary_v12.xlsx
+++ b/outputs/Block2_TimeMachine_Target_Summary_v12.xlsx
@@ -715,7 +715,7 @@
         <v>0.02470934877672151</v>
       </c>
       <c r="E13">
-        <v>0.0001066140499440371</v>
+        <v>0.0001066140499440593</v>
       </c>
       <c r="F13">
         <v>10</v>

--- a/outputs/Block2_TimeMachine_Target_Summary_v12.xlsx
+++ b/outputs/Block2_TimeMachine_Target_Summary_v12.xlsx
@@ -712,10 +712,10 @@
         <v>16</v>
       </c>
       <c r="D13">
-        <v>0.02470934877672151</v>
+        <v>0.0247093487767215</v>
       </c>
       <c r="E13">
-        <v>0.0001066140499440593</v>
+        <v>0.0001066140499440371</v>
       </c>
       <c r="F13">
         <v>10</v>

--- a/outputs/Block2_TimeMachine_Target_Summary_v12.xlsx
+++ b/outputs/Block2_TimeMachine_Target_Summary_v12.xlsx
@@ -712,7 +712,7 @@
         <v>16</v>
       </c>
       <c r="D13">
-        <v>0.0247093487767215</v>
+        <v>0.02470934877672151</v>
       </c>
       <c r="E13">
         <v>0.0001066140499440371</v>

--- a/outputs/Block2_TimeMachine_Target_Summary_v12.xlsx
+++ b/outputs/Block2_TimeMachine_Target_Summary_v12.xlsx
@@ -623,7 +623,7 @@
         <v>0.02858919999999997</v>
       </c>
       <c r="E9">
-        <v>1.71999999992678E-05</v>
+        <v>1.719999999926225E-05</v>
       </c>
       <c r="F9">
         <v>10</v>
@@ -715,7 +715,7 @@
         <v>0.02470934877672151</v>
       </c>
       <c r="E13">
-        <v>0.0001066140499440371</v>
+        <v>0.0001066140499440427</v>
       </c>
       <c r="F13">
         <v>10</v>

--- a/outputs/Block2_TimeMachine_Target_Summary_v12.xlsx
+++ b/outputs/Block2_TimeMachine_Target_Summary_v12.xlsx
@@ -623,7 +623,7 @@
         <v>0.02858919999999997</v>
       </c>
       <c r="E9">
-        <v>1.719999999926225E-05</v>
+        <v>1.71999999992678E-05</v>
       </c>
       <c r="F9">
         <v>10</v>
@@ -715,7 +715,7 @@
         <v>0.02470934877672151</v>
       </c>
       <c r="E13">
-        <v>0.0001066140499440427</v>
+        <v>0.0001066140499440371</v>
       </c>
       <c r="F13">
         <v>10</v>

--- a/outputs/Block2_TimeMachine_Target_Summary_v12.xlsx
+++ b/outputs/Block2_TimeMachine_Target_Summary_v12.xlsx
@@ -623,7 +623,7 @@
         <v>0.02858919999999997</v>
       </c>
       <c r="E9">
-        <v>1.71999999992678E-05</v>
+        <v>1.719999999926225E-05</v>
       </c>
       <c r="F9">
         <v>10</v>
@@ -715,7 +715,7 @@
         <v>0.02470934877672151</v>
       </c>
       <c r="E13">
-        <v>0.0001066140499440371</v>
+        <v>0.0001066140499440316</v>
       </c>
       <c r="F13">
         <v>10</v>

--- a/outputs/Block2_TimeMachine_Target_Summary_v12.xlsx
+++ b/outputs/Block2_TimeMachine_Target_Summary_v12.xlsx
@@ -482,10 +482,10 @@
         <v>16</v>
       </c>
       <c r="D3">
-        <v>0.02177959999999972</v>
+        <v>0.02177959999999971</v>
       </c>
       <c r="E3">
-        <v>0.0002435999999993277</v>
+        <v>0.0002435999999993332</v>
       </c>
       <c r="F3">
         <v>10</v>
@@ -620,10 +620,10 @@
         <v>16</v>
       </c>
       <c r="D9">
-        <v>0.02858919999999997</v>
+        <v>0.02858919999999996</v>
       </c>
       <c r="E9">
-        <v>1.719999999926225E-05</v>
+        <v>1.71999999992678E-05</v>
       </c>
       <c r="F9">
         <v>10</v>
@@ -712,10 +712,10 @@
         <v>16</v>
       </c>
       <c r="D13">
-        <v>0.02470934877672151</v>
+        <v>0.0247093487767215</v>
       </c>
       <c r="E13">
-        <v>0.0001066140499440316</v>
+        <v>0.0001066140499440593</v>
       </c>
       <c r="F13">
         <v>10</v>

--- a/outputs/Block2_TimeMachine_Target_Summary_v12.xlsx
+++ b/outputs/Block2_TimeMachine_Target_Summary_v12.xlsx
@@ -620,10 +620,10 @@
         <v>16</v>
       </c>
       <c r="D9">
-        <v>0.02858919999999996</v>
+        <v>0.02858919999999997</v>
       </c>
       <c r="E9">
-        <v>1.71999999992678E-05</v>
+        <v>1.719999999926225E-05</v>
       </c>
       <c r="F9">
         <v>10</v>
@@ -715,7 +715,7 @@
         <v>0.0247093487767215</v>
       </c>
       <c r="E13">
-        <v>0.0001066140499440593</v>
+        <v>0.0001066140499440649</v>
       </c>
       <c r="F13">
         <v>10</v>

--- a/outputs/Block2_TimeMachine_Target_Summary_v12.xlsx
+++ b/outputs/Block2_TimeMachine_Target_Summary_v12.xlsx
@@ -482,10 +482,10 @@
         <v>16</v>
       </c>
       <c r="D3">
-        <v>0.02177959999999971</v>
+        <v>0.02177959999999972</v>
       </c>
       <c r="E3">
-        <v>0.0002435999999993332</v>
+        <v>0.0002435999999993277</v>
       </c>
       <c r="F3">
         <v>10</v>
@@ -623,7 +623,7 @@
         <v>0.02858919999999997</v>
       </c>
       <c r="E9">
-        <v>1.719999999926225E-05</v>
+        <v>1.71999999992678E-05</v>
       </c>
       <c r="F9">
         <v>10</v>
@@ -712,10 +712,10 @@
         <v>16</v>
       </c>
       <c r="D13">
-        <v>0.0247093487767215</v>
+        <v>0.02470934877672151</v>
       </c>
       <c r="E13">
-        <v>0.0001066140499440649</v>
+        <v>0.0001066140499440593</v>
       </c>
       <c r="F13">
         <v>10</v>

--- a/outputs/Block2_TimeMachine_Target_Summary_v12.xlsx
+++ b/outputs/Block2_TimeMachine_Target_Summary_v12.xlsx
@@ -712,10 +712,10 @@
         <v>16</v>
       </c>
       <c r="D13">
-        <v>0.02470934877672151</v>
+        <v>0.02470934877672152</v>
       </c>
       <c r="E13">
-        <v>0.0001066140499440371</v>
+        <v>0.000106614049944026</v>
       </c>
       <c r="F13">
         <v>10</v>
